--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="509">
   <si>
     <t>Filename</t>
   </si>
@@ -811,229 +811,409 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9084,0.0093,0.0273,0.0077</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9658,0.0002,0.0001,0.0315</t>
-  </si>
-  <si>
-    <t>0.2049,0.0000,0.0001,0.9428</t>
+    <t>0.9463,0.0025,0.0097,0.0113</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9430,0.0002,0.0001,0.0573</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0022,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9990,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0015,0.0002,0.0003</t>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6328,0.0030,0.3024,0.0017</t>
+  </si>
+  <si>
+    <t>0.0174,0.0031,0.9736,0.0022</t>
+  </si>
+  <si>
+    <t>0.4398,0.0002,0.7326,0.0001</t>
+  </si>
+  <si>
+    <t>0.0066,0.0013,0.9879,0.0007</t>
+  </si>
+  <si>
+    <t>0.8675,0.0044,0.0716,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.9938,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.3537,0.0025,0.5026,0.0090</t>
+  </si>
+  <si>
+    <t>0.4243,0.0007,0.5907,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9979,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.0026,0.9919,0.0008</t>
+  </si>
+  <si>
+    <t>0.0062,0.0001,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0133,0.0009,0.9846,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9991,0.0004</t>
+  </si>
+  <si>
+    <t>0.0162,0.9827,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.7555,0.0321,0.1108,0.0019</t>
+  </si>
+  <si>
+    <t>0.0007,0.0008,0.9988,0.0031</t>
+  </si>
+  <si>
+    <t>0.0018,0.9957,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.9880,0.0041,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9616,0.0039,0.0207,0.0007</t>
+  </si>
+  <si>
+    <t>0.0099,0.9844,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.9977,0.0526,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.9890,0.0102,0.0007</t>
+  </si>
+  <si>
+    <t>0.0092,0.0196,0.9688,0.0038</t>
+  </si>
+  <si>
+    <t>0.0048,0.0060,0.9800,0.0017</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0039,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9990,0.0018</t>
+  </si>
+  <si>
+    <t>0.0000,0.9948,0.0001,0.9941</t>
+  </si>
+  <si>
+    <t>0.0007,0.9967,0.0002,0.0059</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0755,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0012,0.9914,0.0009</t>
+  </si>
+  <si>
+    <t>0.0125,0.0001,0.9907,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9993,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9996,0.0006</t>
+  </si>
+  <si>
+    <t>0.9959,0.0032,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0018,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9747,0.0169,0.0068,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.0057,0.9989,0.0010</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.8997,0.1263,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0017,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9910,0.9794,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0042,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0441,0.9979,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.9953,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0032,0.9954,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9914,0.0001,0.0063,0.0002</t>
+  </si>
+  <si>
+    <t>0.0526,0.0012,0.9522,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0058,0.9996,0.0021</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.3244,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9821,0.9654,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9873,0.9087,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0005,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0077,0.9993</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0005,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.6449,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.9925,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.2575,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9916,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9866,0.6444,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.2426,0.0054,0.6699,0.0014</t>
-  </si>
-  <si>
-    <t>0.0045,0.0012,0.9910,0.0006</t>
-  </si>
-  <si>
-    <t>0.0499,0.0010,0.9623,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.0011,0.9918,0.0008</t>
-  </si>
-  <si>
-    <t>0.9321,0.0005,0.0543,0.0006</t>
+    <t>0.9993,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9872,0.0149,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9910,0.0026,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9941,0.0031,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9922,0.0086,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0019,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0003,0.9979,0.0007</t>
+  </si>
+  <si>
+    <t>0.0190,0.0007,0.9715,0.0021</t>
+  </si>
+  <si>
+    <t>0.9809,0.0005,0.0050,0.0008</t>
+  </si>
+  <si>
+    <t>0.0212,0.0002,0.9766,0.0007</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0005,0.9985,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.0042,0.9926,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.3838,0.0005,0.6057,0.0018</t>
-  </si>
-  <si>
-    <t>0.0396,0.0004,0.9646,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9984,0.0004</t>
-  </si>
-  <si>
-    <t>0.0205,0.0011,0.9714,0.0006</t>
-  </si>
-  <si>
-    <t>0.0393,0.0001,0.9733,0.0002</t>
-  </si>
-  <si>
-    <t>0.0038,0.0001,0.9913,0.0014</t>
-  </si>
-  <si>
-    <t>0.0180,0.0000,0.9897,0.0001</t>
-  </si>
-  <si>
-    <t>0.2315,0.8147,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9404,0.0321,0.0147,0.0006</t>
-  </si>
-  <si>
-    <t>0.0010,0.0004,0.9990,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.9980,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.9784,0.0068,0.0009,0.0032</t>
-  </si>
-  <si>
-    <t>0.9459,0.0026,0.0375,0.0006</t>
-  </si>
-  <si>
-    <t>0.0378,0.9556,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.9973,0.0084,0.0002</t>
-  </si>
-  <si>
-    <t>0.0048,0.9805,0.0104,0.0004</t>
-  </si>
-  <si>
-    <t>0.0168,0.0055,0.9564,0.0051</t>
-  </si>
-  <si>
-    <t>0.0132,0.0087,0.9673,0.0010</t>
-  </si>
-  <si>
-    <t>0.0309,0.0003,0.9541,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0482,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9991,0.0005</t>
-  </si>
-  <si>
-    <t>0.0080,0.5703,0.0005,0.9238</t>
-  </si>
-  <si>
-    <t>0.0017,0.9895,0.0001,0.0126</t>
-  </si>
-  <si>
-    <t>0.0009,0.9970,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.1862,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0048,0.0025,0.9678,0.0289</t>
-  </si>
-  <si>
-    <t>0.1122,0.0001,0.9158,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0029,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0004,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0017,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.0007,0.9986,0.0004</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9112,0.1199,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9930,0.9497,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0140,0.9948,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9996,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9991,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9942,0.0005,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.0141,0.0008,0.9864,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0013,0.9993,0.0024</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.9731,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9938,0.7902,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.7105,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9968,0.5992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0005,0.9997</t>
+    <t>0.0016,0.9955,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.9983,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0454,0.9571,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.6980,0.0019,0.1969,0.0049</t>
+  </si>
+  <si>
+    <t>0.9526,0.0000,0.0406,0.0005</t>
+  </si>
+  <si>
+    <t>0.9419,0.0014,0.0221,0.0037</t>
+  </si>
+  <si>
+    <t>0.9528,0.0114,0.0075,0.0015</t>
+  </si>
+  <si>
+    <t>0.0001,0.1015,0.0007,0.9983</t>
+  </si>
+  <si>
+    <t>0.0004,0.9988,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.5889,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4851,0.5769,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9275,0.0775,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0015,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9924,0.0001,0.0001,0.0072</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9956,0.0009,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9932,0.0020,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9728,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9972,0.9599,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0094,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.0544,0.9853,0.0005</t>
+  </si>
+  <si>
+    <t>0.9935,0.0002,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.2909,0.0048,0.5792,0.0058</t>
+  </si>
+  <si>
+    <t>0.1530,0.0001,0.8888,0.0001</t>
+  </si>
+  <si>
+    <t>0.8172,0.0135,0.0214,0.0362</t>
+  </si>
+  <si>
+    <t>0.0092,0.0005,0.0003,0.9963</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.0000,1.0000</t>
@@ -1042,493 +1222,325 @@
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0001,0.0019,0.9996</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.4003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9553,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.9778,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9955,0.9935,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.8881,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9814,0.6859,0.0000</t>
-  </si>
-  <si>
-    <t>0.9939,0.0045,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0003,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9866,0.0093,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0027,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0047,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9907,0.0080,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0014,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0059,0.0002,0.9961,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0007,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.9739,0.0021,0.0022,0.0017</t>
-  </si>
-  <si>
-    <t>0.0056,0.0003,0.9916,0.0011</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9984,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.9987,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0236,0.9732,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.8283,0.0049,0.0952,0.0045</t>
-  </si>
-  <si>
-    <t>0.7196,0.0005,0.2820,0.0007</t>
-  </si>
-  <si>
-    <t>0.9091,0.0269,0.0020,0.0031</t>
-  </si>
-  <si>
-    <t>0.0177,0.0087,0.9510,0.0116</t>
-  </si>
-  <si>
-    <t>0.0002,0.4713,0.0017,0.9942</t>
-  </si>
-  <si>
-    <t>0.0007,0.9981,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0000,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.9899,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0622,0.9389,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.2108,0.8076,0.0034,0.0005</t>
-  </si>
-  <si>
-    <t>0.9965,0.0016,0.0002,0.0001</t>
+    <t>0.0001,0.9938,0.4970,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.0114,0.9771,0.0026,0.0079</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0405,0.9651,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0002,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0802,0.0001,0.0000,0.9739</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0038,0.9964,0.0050</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0001,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.0160,0.9797,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9869,0.0020,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.9767,0.0053,0.0046,0.0016</t>
+  </si>
+  <si>
+    <t>0.1510,0.1733,0.1718,0.0137</t>
+  </si>
+  <si>
+    <t>0.2061,0.5908,0.1313,0.0024</t>
+  </si>
+  <si>
+    <t>0.9852,0.0027,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0001,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9961,0.0003,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9973,0.0005,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.7047,0.9853,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.8652,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0544,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0013,0.9957,0.0003</t>
-  </si>
-  <si>
-    <t>0.9974,0.0003,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.2139,0.0005,0.7821,0.0008</t>
-  </si>
-  <si>
-    <t>0.0986,0.0001,0.9418,0.0001</t>
-  </si>
-  <si>
-    <t>0.9250,0.0021,0.0313,0.0054</t>
-  </si>
-  <si>
-    <t>0.1914,0.0000,0.0000,0.9597</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.5157,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.0016,0.9958,0.0008,0.0013</t>
-  </si>
-  <si>
-    <t>0.9970,0.0001,0.0000,0.0025</t>
-  </si>
-  <si>
-    <t>0.0053,0.9938,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.5724,0.0019,0.0008,0.3673</t>
-  </si>
-  <si>
-    <t>0.0007,0.0040,0.9980,0.0031</t>
-  </si>
-  <si>
-    <t>0.9886,0.0003,0.0029,0.0016</t>
-  </si>
-  <si>
-    <t>0.9981,0.0000,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0283,0.9686,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.9812,0.0006,0.0006,0.0067</t>
-  </si>
-  <si>
-    <t>0.9788,0.0065,0.0023,0.0018</t>
-  </si>
-  <si>
-    <t>0.0916,0.5136,0.0605,0.0572</t>
-  </si>
-  <si>
-    <t>0.5112,0.0169,0.3866,0.0013</t>
-  </si>
-  <si>
-    <t>0.9964,0.0002,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9924,0.0014,0.0004,0.0020</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.6595,0.2471,0.0004,0.0024</t>
-  </si>
-  <si>
-    <t>0.1283,0.9117,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.3186,0.7618,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9383,0.0015,0.0166,0.0074</t>
-  </si>
-  <si>
-    <t>0.9917,0.0063,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9895,0.0020,0.0011,0.0030</t>
-  </si>
-  <si>
-    <t>0.9902,0.0048,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9717,0.0029,0.0047,0.0068</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.9708,0.0158,0.0053,0.0026</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0013,0.9963,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.2073,0.9946,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0376,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0950,0.0004,0.8820,0.0014</t>
-  </si>
-  <si>
-    <t>0.0018,0.0031,0.9936,0.0004</t>
-  </si>
-  <si>
-    <t>0.7005,0.0071,0.0979,0.0275</t>
-  </si>
-  <si>
-    <t>0.0126,0.0143,0.9649,0.0003</t>
-  </si>
-  <si>
-    <t>0.0249,0.2949,0.4746,0.0017</t>
-  </si>
-  <si>
-    <t>0.4717,0.0220,0.4979,0.0010</t>
-  </si>
-  <si>
-    <t>0.7712,0.0079,0.0127,0.0726</t>
-  </si>
-  <si>
-    <t>0.2705,0.0375,0.5130,0.0075</t>
-  </si>
-  <si>
-    <t>0.0011,0.9980,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9993,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.5091,0.6035,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.0682,0.9431,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9985,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9298,0.0092,0.0124,0.0021</t>
-  </si>
-  <si>
-    <t>0.9329,0.0006,0.0466,0.0016</t>
-  </si>
-  <si>
-    <t>0.7092,0.0015,0.0070,0.1330</t>
-  </si>
-  <si>
-    <t>0.8282,0.0199,0.0532,0.0132</t>
-  </si>
-  <si>
-    <t>0.0404,0.0006,0.9545,0.0017</t>
-  </si>
-  <si>
-    <t>0.0012,0.0007,0.9980,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0035,0.9977,0.0006</t>
-  </si>
-  <si>
-    <t>0.0252,0.2043,0.8881,0.0036</t>
-  </si>
-  <si>
-    <t>0.0277,0.0032,0.9584,0.0002</t>
-  </si>
-  <si>
-    <t>0.0059,0.0537,0.9392,0.0008</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0010,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9939,0.0010,0.0002,0.0018</t>
-  </si>
-  <si>
-    <t>0.9961,0.0026,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9904,0.0039,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9948,0.0025,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9995,0.0015</t>
-  </si>
-  <si>
-    <t>0.0773,0.1738,0.5308,0.0041</t>
-  </si>
-  <si>
-    <t>0.9484,0.0002,0.0196,0.0056</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0099,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.8240,0.9315,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0540,0.0060,0.9188,0.0029</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0025,0.9965,0.0016</t>
-  </si>
-  <si>
-    <t>0.0002,0.0051,0.9991,0.0003</t>
-  </si>
-  <si>
-    <t>0.8351,0.0014,0.0971,0.0052</t>
-  </si>
-  <si>
-    <t>0.9674,0.0003,0.0220,0.0005</t>
-  </si>
-  <si>
-    <t>0.9939,0.0002,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9797,0.0173,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0019,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.0293,0.9828,0.0010</t>
-  </si>
-  <si>
-    <t>0.0005,0.0478,0.9935,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.8396,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0167,0.0056,0.9577,0.0021</t>
-  </si>
-  <si>
-    <t>0.0011,0.0004,0.9978,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.0012,0.9411,0.0905</t>
-  </si>
-  <si>
-    <t>0.0443,0.0114,0.9090,0.0137</t>
-  </si>
-  <si>
-    <t>0.0241,0.0089,0.9067,0.0197</t>
-  </si>
-  <si>
-    <t>0.9795,0.0000,0.0005,0.0134</t>
-  </si>
-  <si>
-    <t>0.0007,0.0009,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0038,0.0000,0.0000,0.9991</t>
-  </si>
-  <si>
-    <t>0.9852,0.0010,0.0011,0.0023</t>
+    <t>0.9899,0.0014,0.0008,0.0046</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0002,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.8243,0.0792,0.0003,0.0039</t>
+  </si>
+  <si>
+    <t>0.3491,0.7783,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.6014,0.4272,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0304,0.0066,0.9625,0.0011</t>
+  </si>
+  <si>
+    <t>0.9803,0.0133,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9901,0.0009,0.0002,0.0040</t>
+  </si>
+  <si>
+    <t>0.9902,0.0068,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9744,0.0077,0.0075,0.0020</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9829,0.0077,0.0035,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0175,0.9769,0.0043</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0337,0.0868,0.8925,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0021,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0424,0.0126,0.9141,0.0038</t>
+  </si>
+  <si>
+    <t>0.0031,0.0037,0.9900,0.0024</t>
+  </si>
+  <si>
+    <t>0.1452,0.5491,0.0455,0.0489</t>
+  </si>
+  <si>
+    <t>0.3509,0.0096,0.6253,0.0009</t>
+  </si>
+  <si>
+    <t>0.1688,0.3340,0.1477,0.0016</t>
+  </si>
+  <si>
+    <t>0.4148,0.0049,0.6556,0.0007</t>
+  </si>
+  <si>
+    <t>0.6611,0.0392,0.0261,0.0603</t>
+  </si>
+  <si>
+    <t>0.1112,0.0021,0.9053,0.0004</t>
+  </si>
+  <si>
+    <t>0.0067,0.9919,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0816,0.9366,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.1663,0.8776,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0837,0.9109,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.5147,0.3599,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.9756,0.0001,0.0124,0.0009</t>
+  </si>
+  <si>
+    <t>0.9385,0.0006,0.0024,0.0171</t>
+  </si>
+  <si>
+    <t>0.6861,0.0303,0.2118,0.0081</t>
+  </si>
+  <si>
+    <t>0.7820,0.0061,0.0957,0.0220</t>
+  </si>
+  <si>
+    <t>0.0045,0.0004,0.9941,0.0016</t>
+  </si>
+  <si>
+    <t>0.0023,0.0055,0.9843,0.0025</t>
+  </si>
+  <si>
+    <t>0.0049,0.0492,0.9715,0.0024</t>
+  </si>
+  <si>
+    <t>0.0009,0.0048,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.5224,0.8225,0.0006</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9792,0.0195,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9767,0.0064,0.0006,0.0046</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9896,0.0078,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9927,0.0057,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0015,0.9984,0.0009</t>
+  </si>
+  <si>
+    <t>0.0167,0.0967,0.8432,0.0042</t>
+  </si>
+  <si>
+    <t>0.9874,0.0004,0.0031,0.0024</t>
+  </si>
+  <si>
+    <t>0.0041,0.0004,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0060,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9501,0.9102,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0005,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0003,0.9951,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0008,0.9964,0.0014</t>
+  </si>
+  <si>
+    <t>0.0016,0.0055,0.9929,0.0011</t>
+  </si>
+  <si>
+    <t>0.1552,0.0301,0.5380,0.0095</t>
+  </si>
+  <si>
+    <t>0.9737,0.0003,0.0141,0.0006</t>
+  </si>
+  <si>
+    <t>0.9809,0.0008,0.0024,0.0021</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9913,0.0067,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9925,0.0050,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9971,0.0019,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0010,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0034,0.0235,0.9749,0.0015</t>
+  </si>
+  <si>
+    <t>0.0001,0.0016,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.6362,0.9279,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.0077,0.9926,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0120,0.0005,0.9495,0.0073</t>
+  </si>
+  <si>
+    <t>0.1850,0.0040,0.7871,0.0021</t>
+  </si>
+  <si>
+    <t>0.1732,0.0215,0.6783,0.0069</t>
+  </si>
+  <si>
+    <t>0.9649,0.0000,0.0006,0.0314</t>
+  </si>
+  <si>
+    <t>0.0008,0.0018,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0190,0.0001,0.0001,0.9957</t>
+  </si>
+  <si>
+    <t>0.9867,0.0001,0.0001,0.0094</t>
   </si>
 </sst>
 </file>
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2079,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
         <v>276</v>
@@ -2572,7 +2584,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2905,10 +2917,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2922,7 +2934,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2933,10 +2945,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2978,7 +2990,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3045,10 +3057,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3073,10 +3085,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3118,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3132,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>358</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>275</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>281</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3549,7 +3561,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
         <v>374</v>
@@ -3661,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
         <v>382</v>
@@ -3916,7 +3928,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>340</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3955,7 +3967,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>402</v>
@@ -4039,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>408</v>
@@ -4056,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>358</v>
+        <v>409</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4084,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4151,10 +4163,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4165,10 +4177,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4196,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>275</v>
+        <v>419</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4333,10 +4345,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4347,10 +4359,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4364,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4378,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4392,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4571,10 +4583,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4588,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4613,10 +4625,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4630,7 +4642,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4644,7 +4656,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4658,7 +4670,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4672,7 +4684,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4686,7 +4698,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4714,7 +4726,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4781,10 +4793,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4798,7 +4810,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4812,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4826,7 +4838,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4851,10 +4863,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5036,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5131,10 +5143,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5190,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>464</v>
+        <v>496</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5400,7 +5412,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5442,7 +5454,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>341</v>
+        <v>401</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>341</v>
+        <v>401</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="508">
   <si>
     <t>Filename</t>
   </si>
@@ -808,739 +808,736 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9463,0.0025,0.0097,0.0113</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9802,0.0037,0.0036,0.0017</t>
   </si>
   <si>
     <t>0.0002,0.0001,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.9430,0.0002,0.0001,0.0573</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.0003,0.9991</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0022,0.0001,0.0001</t>
+    <t>0.8453,0.0004,0.0004,0.1694</t>
+  </si>
+  <si>
+    <t>0.0018,0.0000,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0009,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6328,0.0030,0.3024,0.0017</t>
-  </si>
-  <si>
-    <t>0.0174,0.0031,0.9736,0.0022</t>
-  </si>
-  <si>
-    <t>0.4398,0.0002,0.7326,0.0001</t>
-  </si>
-  <si>
-    <t>0.0066,0.0013,0.9879,0.0007</t>
-  </si>
-  <si>
-    <t>0.8675,0.0044,0.0716,0.0016</t>
+    <t>0.9832,0.0006,0.0071,0.0002</t>
+  </si>
+  <si>
+    <t>0.0053,0.0007,0.9917,0.0013</t>
+  </si>
+  <si>
+    <t>0.2689,0.0097,0.7560,0.0003</t>
+  </si>
+  <si>
+    <t>0.0022,0.0023,0.9941,0.0005</t>
+  </si>
+  <si>
+    <t>0.9856,0.0002,0.0077,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0086,0.9880,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0006</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.9938,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.3537,0.0025,0.5026,0.0090</t>
-  </si>
-  <si>
-    <t>0.4243,0.0007,0.5907,0.0007</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9979,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.0026,0.9919,0.0008</t>
-  </si>
-  <si>
-    <t>0.0062,0.0001,0.9957,0.0001</t>
-  </si>
-  <si>
-    <t>0.0133,0.0009,0.9846,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9991,0.0004</t>
-  </si>
-  <si>
-    <t>0.0162,0.9827,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.7555,0.0321,0.1108,0.0019</t>
-  </si>
-  <si>
-    <t>0.0007,0.0008,0.9988,0.0031</t>
-  </si>
-  <si>
-    <t>0.0018,0.9957,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9880,0.0041,0.0008,0.0015</t>
-  </si>
-  <si>
-    <t>0.9616,0.0039,0.0207,0.0007</t>
-  </si>
-  <si>
-    <t>0.0099,0.9844,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.9977,0.0526,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.9890,0.0102,0.0007</t>
-  </si>
-  <si>
-    <t>0.0092,0.0196,0.9688,0.0038</t>
-  </si>
-  <si>
-    <t>0.0048,0.0060,0.9800,0.0017</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0039,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9990,0.0018</t>
-  </si>
-  <si>
-    <t>0.0000,0.9948,0.0001,0.9941</t>
-  </si>
-  <si>
-    <t>0.0007,0.9967,0.0002,0.0059</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0755,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.0012,0.9914,0.0009</t>
-  </si>
-  <si>
-    <t>0.0125,0.0001,0.9907,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9993,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9996,0.0006</t>
-  </si>
-  <si>
-    <t>0.9959,0.0032,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0018,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9747,0.0169,0.0068,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.0057,0.9989,0.0010</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.8997,0.1263,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9966,0.0017,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9910,0.9794,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0042,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0441,0.9979,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9953,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0032,0.9954,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9914,0.0001,0.0063,0.0002</t>
-  </si>
-  <si>
-    <t>0.0526,0.0012,0.9522,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0058,0.9996,0.0021</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.3244,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9821,0.9654,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9873,0.9087,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0005,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0077,0.9993</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0005,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.6449,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.9925,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.2575,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9916,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9866,0.6444,0.0000</t>
+    <t>0.6586,0.0004,0.3055,0.0020</t>
+  </si>
+  <si>
+    <t>0.5422,0.0025,0.4097,0.0013</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.9973,0.0020</t>
+  </si>
+  <si>
+    <t>0.0024,0.0033,0.9914,0.0005</t>
+  </si>
+  <si>
+    <t>0.0259,0.0002,0.9748,0.0009</t>
+  </si>
+  <si>
+    <t>0.0370,0.0001,0.9646,0.0005</t>
+  </si>
+  <si>
+    <t>0.0118,0.0001,0.9889,0.0007</t>
+  </si>
+  <si>
+    <t>0.0299,0.9739,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.8642,0.0207,0.0686,0.0020</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9996,0.0039</t>
+  </si>
+  <si>
+    <t>0.0027,0.9924,0.0052,0.0001</t>
+  </si>
+  <si>
+    <t>0.9949,0.0016,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9919,0.0018,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.0263,0.9673,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.9926,0.1803,0.0001</t>
+  </si>
+  <si>
+    <t>0.0077,0.9567,0.0355,0.0015</t>
+  </si>
+  <si>
+    <t>0.0034,0.0025,0.9869,0.0015</t>
+  </si>
+  <si>
+    <t>0.0017,0.0139,0.9923,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0212,0.9975,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9986,0.0050,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9962,0.0077</t>
+  </si>
+  <si>
+    <t>0.0104,0.1244,0.0002,0.9786</t>
+  </si>
+  <si>
+    <t>0.0004,0.9980,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.0005,0.9974,0.0058,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9993,0.0015</t>
+  </si>
+  <si>
+    <t>0.0003,0.0280,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0004,0.9939,0.0027</t>
+  </si>
+  <si>
+    <t>0.0220,0.0001,0.9870,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9994,0.0022</t>
+  </si>
+  <si>
+    <t>0.9964,0.0027,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0010,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9922,0.0042,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.0020,0.9984,0.0033</t>
+  </si>
+  <si>
+    <t>0.9972,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.8514,0.1554,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9975,0.0012,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9912,0.7616,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0356,0.9994,0.0006</t>
+  </si>
+  <si>
+    <t>0.0017,0.0114,0.9912,0.0017</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9877,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9988,0.0004</t>
+  </si>
+  <si>
+    <t>0.0039,0.9945,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.2803,0.0007,0.7488,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.0033,0.9987,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9945,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9935,0.8055,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.7228,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9920,0.9822,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0005,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0014,0.9996</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0003,0.9995</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.9921,0.8834,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9889,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9848,0.7100,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9961,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9929,0.9897,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.1079,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9872,0.0149,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9910,0.0026,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9941,0.0031,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9922,0.0086,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0000,0.0000</t>
+    <t>0.9934,0.0061,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9967,0.0002,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9908,0.0051,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9848,0.0072,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.9966,0.0029,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9857,0.0127,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0018,0.0002,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.0008,0.9965,0.0003</t>
+  </si>
+  <si>
+    <t>0.9325,0.0066,0.0068,0.0046</t>
+  </si>
+  <si>
+    <t>0.2166,0.0002,0.8041,0.0007</t>
+  </si>
+  <si>
+    <t>0.0004,0.9986,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.9970,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0245,0.9703,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.4737,0.0008,0.4734,0.0020</t>
+  </si>
+  <si>
+    <t>0.9468,0.0005,0.0509,0.0003</t>
+  </si>
+  <si>
+    <t>0.8601,0.0104,0.0194,0.0124</t>
+  </si>
+  <si>
+    <t>0.8734,0.0254,0.0174,0.0117</t>
+  </si>
+  <si>
+    <t>0.0072,0.0727,0.0039,0.9836</t>
+  </si>
+  <si>
+    <t>0.0008,0.9976,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9956,0.9669,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.5507,0.5559,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.5207,0.5051,0.0117,0.0008</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.4812,0.9641,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9912,0.9872,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0178,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0087,0.9938,0.0011</t>
+  </si>
+  <si>
+    <t>0.9939,0.0006,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0498,0.0039,0.9295,0.0016</t>
+  </si>
+  <si>
+    <t>0.5218,0.0001,0.6018,0.0002</t>
+  </si>
+  <si>
+    <t>0.9573,0.0009,0.0062,0.0052</t>
+  </si>
+  <si>
+    <t>0.0034,0.0003,0.0001,0.9986</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9933,0.4926,0.0000</t>
+  </si>
+  <si>
+    <t>0.9942,0.0001,0.0000,0.0027</t>
+  </si>
+  <si>
+    <t>0.0017,0.9955,0.0005,0.0023</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0083,0.9891,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0002,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.6577,0.0001,0.0000,0.4955</t>
+  </si>
+  <si>
+    <t>0.0001,0.0032,0.9992,0.0037</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0162,0.9839,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9923,0.0003,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.9926,0.0009,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.3109,0.1354,0.0796,0.0127</t>
+  </si>
+  <si>
+    <t>0.4161,0.0395,0.3138,0.0028</t>
+  </si>
+  <si>
+    <t>0.9968,0.0003,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0006,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0011,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.8473,0.1231,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.0504,0.9590,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.3754,0.6970,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9940,0.0015,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9630,0.0336,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0003,0.0001,0.0030</t>
+  </si>
+  <si>
+    <t>0.9961,0.0016,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9504,0.0188,0.0095,0.0089</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.9953,0.0021,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0071,0.0161,0.9715,0.0033</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.2997,0.9901,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0128,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0000,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0704,0.0024,0.8901,0.0046</t>
+  </si>
+  <si>
+    <t>0.0180,0.0007,0.9776,0.0011</t>
+  </si>
+  <si>
+    <t>0.0118,0.0052,0.9775,0.0007</t>
+  </si>
+  <si>
+    <t>0.0144,0.0034,0.9733,0.0003</t>
+  </si>
+  <si>
+    <t>0.0432,0.0526,0.8150,0.0020</t>
+  </si>
+  <si>
+    <t>0.7309,0.0148,0.2595,0.0011</t>
+  </si>
+  <si>
+    <t>0.9547,0.0023,0.0184,0.0012</t>
+  </si>
+  <si>
+    <t>0.0864,0.0009,0.9096,0.0012</t>
+  </si>
+  <si>
+    <t>0.0004,0.9989,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4036,0.6845,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.0186,0.9804,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0366,0.9537,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9665,0.0063,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.8963,0.0012,0.0734,0.0025</t>
+  </si>
+  <si>
+    <t>0.9235,0.0013,0.0212,0.0090</t>
+  </si>
+  <si>
+    <t>0.6496,0.0088,0.2374,0.0192</t>
+  </si>
+  <si>
+    <t>0.1056,0.0013,0.8415,0.0058</t>
+  </si>
+  <si>
+    <t>0.0010,0.0007,0.9976,0.0017</t>
+  </si>
+  <si>
+    <t>0.0006,0.0012,0.9962,0.0004</t>
+  </si>
+  <si>
+    <t>0.0099,0.0677,0.9603,0.0011</t>
+  </si>
+  <si>
+    <t>0.0065,0.0015,0.9886,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.9627,0.1930,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9954,0.0021,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9920,0.0005,0.0000,0.0020</t>
+  </si>
+  <si>
+    <t>0.9963,0.0019,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0001,0.0002</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9963,0.0019,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0003,0.9979,0.0007</t>
-  </si>
-  <si>
-    <t>0.0190,0.0007,0.9715,0.0021</t>
-  </si>
-  <si>
-    <t>0.9809,0.0005,0.0050,0.0008</t>
-  </si>
-  <si>
-    <t>0.0212,0.0002,0.9766,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9955,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.9983,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0454,0.9571,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.6980,0.0019,0.1969,0.0049</t>
-  </si>
-  <si>
-    <t>0.9526,0.0000,0.0406,0.0005</t>
-  </si>
-  <si>
-    <t>0.9419,0.0014,0.0221,0.0037</t>
-  </si>
-  <si>
-    <t>0.9528,0.0114,0.0075,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.1015,0.0007,0.9983</t>
-  </si>
-  <si>
-    <t>0.0004,0.9988,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.5889,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4851,0.5769,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9275,0.0775,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9971,0.0015,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9924,0.0001,0.0001,0.0072</t>
+    <t>0.0016,0.0013,0.9965,0.0013</t>
+  </si>
+  <si>
+    <t>0.1442,0.2685,0.3563,0.0028</t>
+  </si>
+  <si>
+    <t>0.8769,0.0023,0.0247,0.0346</t>
+  </si>
+  <si>
+    <t>0.0016,0.0009,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0059,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.3773,0.9117,0.0003</t>
+  </si>
+  <si>
+    <t>0.0042,0.0005,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0240,0.0004,0.9672,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0021,0.9983,0.0012</t>
+  </si>
+  <si>
+    <t>0.0010,0.0038,0.9950,0.0025</t>
+  </si>
+  <si>
+    <t>0.9164,0.0009,0.0452,0.0029</t>
+  </si>
+  <si>
+    <t>0.9758,0.0002,0.0115,0.0008</t>
+  </si>
+  <si>
+    <t>0.9892,0.0006,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9950,0.0012,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9820,0.0161,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0030,0.0006,0.0002</t>
   </si>
   <si>
     <t>0.9991,0.0001,0.0001,0.0002</t>
   </si>
   <si>
-    <t>0.9984,0.0001,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9956,0.0009,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9932,0.0020,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9728,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.9599,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0094,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.0544,0.9853,0.0005</t>
-  </si>
-  <si>
-    <t>0.9935,0.0002,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.2909,0.0048,0.5792,0.0058</t>
-  </si>
-  <si>
-    <t>0.1530,0.0001,0.8888,0.0001</t>
-  </si>
-  <si>
-    <t>0.8172,0.0135,0.0214,0.0362</t>
-  </si>
-  <si>
-    <t>0.0092,0.0005,0.0003,0.9963</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9938,0.4970,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0114,0.9771,0.0026,0.0079</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0405,0.9651,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0802,0.0001,0.0000,0.9739</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.0038,0.9964,0.0050</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0001,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.0160,0.9797,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9869,0.0020,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.9767,0.0053,0.0046,0.0016</t>
-  </si>
-  <si>
-    <t>0.1510,0.1733,0.1718,0.0137</t>
-  </si>
-  <si>
-    <t>0.2061,0.5908,0.1313,0.0024</t>
-  </si>
-  <si>
-    <t>0.9852,0.0027,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9899,0.0014,0.0008,0.0046</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0002,0.0005,0.0016</t>
-  </si>
-  <si>
-    <t>0.8243,0.0792,0.0003,0.0039</t>
-  </si>
-  <si>
-    <t>0.3491,0.7783,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.6014,0.4272,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0304,0.0066,0.9625,0.0011</t>
-  </si>
-  <si>
-    <t>0.9803,0.0133,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9901,0.0009,0.0002,0.0040</t>
-  </si>
-  <si>
-    <t>0.9902,0.0068,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9744,0.0077,0.0075,0.0020</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9829,0.0077,0.0035,0.0012</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0043,0.0175,0.9769,0.0043</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0337,0.0868,0.8925,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0021,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0424,0.0126,0.9141,0.0038</t>
-  </si>
-  <si>
-    <t>0.0031,0.0037,0.9900,0.0024</t>
-  </si>
-  <si>
-    <t>0.1452,0.5491,0.0455,0.0489</t>
-  </si>
-  <si>
-    <t>0.3509,0.0096,0.6253,0.0009</t>
-  </si>
-  <si>
-    <t>0.1688,0.3340,0.1477,0.0016</t>
-  </si>
-  <si>
-    <t>0.4148,0.0049,0.6556,0.0007</t>
-  </si>
-  <si>
-    <t>0.6611,0.0392,0.0261,0.0603</t>
-  </si>
-  <si>
-    <t>0.1112,0.0021,0.9053,0.0004</t>
-  </si>
-  <si>
-    <t>0.0067,0.9919,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0816,0.9366,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.1663,0.8776,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0837,0.9109,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.5147,0.3599,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.9756,0.0001,0.0124,0.0009</t>
-  </si>
-  <si>
-    <t>0.9385,0.0006,0.0024,0.0171</t>
-  </si>
-  <si>
-    <t>0.6861,0.0303,0.2118,0.0081</t>
-  </si>
-  <si>
-    <t>0.7820,0.0061,0.0957,0.0220</t>
-  </si>
-  <si>
-    <t>0.0045,0.0004,0.9941,0.0016</t>
-  </si>
-  <si>
-    <t>0.0023,0.0055,0.9843,0.0025</t>
-  </si>
-  <si>
-    <t>0.0049,0.0492,0.9715,0.0024</t>
-  </si>
-  <si>
-    <t>0.0009,0.0048,0.9958,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.5224,0.8225,0.0006</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9792,0.0195,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9767,0.0064,0.0006,0.0046</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9896,0.0078,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9927,0.0057,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0015,0.9984,0.0009</t>
-  </si>
-  <si>
-    <t>0.0167,0.0967,0.8432,0.0042</t>
-  </si>
-  <si>
-    <t>0.9874,0.0004,0.0031,0.0024</t>
-  </si>
-  <si>
-    <t>0.0041,0.0004,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0060,0.9960,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9501,0.9102,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0005,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0003,0.9951,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0008,0.9964,0.0014</t>
-  </si>
-  <si>
-    <t>0.0016,0.0055,0.9929,0.0011</t>
-  </si>
-  <si>
-    <t>0.1552,0.0301,0.5380,0.0095</t>
-  </si>
-  <si>
-    <t>0.9737,0.0003,0.0141,0.0006</t>
-  </si>
-  <si>
-    <t>0.9809,0.0008,0.0024,0.0021</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9913,0.0067,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9925,0.0050,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9971,0.0019,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0010,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0034,0.0235,0.9749,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.6362,0.9279,0.0013</t>
-  </si>
-  <si>
-    <t>0.0011,0.0077,0.9926,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9991,0.0003</t>
-  </si>
-  <si>
-    <t>0.0120,0.0005,0.9495,0.0073</t>
-  </si>
-  <si>
-    <t>0.1850,0.0040,0.7871,0.0021</t>
-  </si>
-  <si>
-    <t>0.1732,0.0215,0.6783,0.0069</t>
-  </si>
-  <si>
-    <t>0.9649,0.0000,0.0006,0.0314</t>
-  </si>
-  <si>
-    <t>0.0008,0.0018,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.0190,0.0001,0.0001,0.9957</t>
-  </si>
-  <si>
-    <t>0.9867,0.0001,0.0001,0.0094</t>
+    <t>0.9978,0.0015,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9956,0.0017,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.0129,0.1131,0.8278,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0024,0.9994,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9036,0.9772,0.0001</t>
+  </si>
+  <si>
+    <t>0.0040,0.0094,0.9754,0.0088</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0181,0.0005,0.7934,0.0485</t>
+  </si>
+  <si>
+    <t>0.0217,0.0007,0.9674,0.0015</t>
+  </si>
+  <si>
+    <t>0.0179,0.0014,0.9669,0.0025</t>
+  </si>
+  <si>
+    <t>0.9190,0.0000,0.0001,0.1419</t>
+  </si>
+  <si>
+    <t>0.0000,0.0259,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0063,0.0000,0.0000,0.9986</t>
+  </si>
+  <si>
+    <t>0.9952,0.0003,0.0002,0.0008</t>
   </si>
 </sst>
 </file>
@@ -1926,7 +1923,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1940,7 +1937,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1954,7 +1951,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1968,7 +1965,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1982,7 +1979,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1996,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2010,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2024,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2038,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2052,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2066,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2080,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2094,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2108,7 +2105,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2122,7 +2119,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2136,7 +2133,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2150,7 +2147,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2164,7 +2161,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2178,7 +2175,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2192,7 +2189,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2206,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2220,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2231,10 +2228,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2245,10 +2242,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2262,7 +2259,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2276,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2290,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2304,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2318,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2332,7 +2329,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2346,7 +2343,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2360,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2374,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2388,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2402,7 +2399,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2416,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2430,7 +2427,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2444,7 +2441,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2458,7 +2455,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2472,7 +2469,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2486,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2500,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2514,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2528,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2539,10 +2536,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2556,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2570,7 +2567,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2584,7 +2581,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2598,7 +2595,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2612,7 +2609,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2626,7 +2623,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2640,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2654,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2668,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2682,7 +2679,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2696,7 +2693,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2710,7 +2707,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2724,7 +2721,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2738,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2752,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2766,7 +2763,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2780,7 +2777,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2794,7 +2791,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2808,7 +2805,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2822,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2836,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2850,7 +2847,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2864,7 +2861,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2878,7 +2875,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2892,7 +2889,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2906,7 +2903,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2917,10 +2914,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2934,7 +2931,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2945,10 +2942,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2962,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2976,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2990,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3004,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3018,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3032,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3046,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3060,7 +3057,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3074,7 +3071,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3085,10 +3082,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3102,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3116,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3127,10 +3124,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3144,7 +3141,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3158,7 +3155,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3172,7 +3169,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3186,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3200,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3214,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3228,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3242,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3256,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3270,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3284,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3298,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3312,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3326,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3340,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3354,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>361</v>
+        <v>277</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3368,7 +3365,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3382,7 +3379,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3396,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3410,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3424,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>366</v>
+        <v>313</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3438,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>366</v>
+        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3452,7 +3449,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3466,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3480,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3494,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3508,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3519,10 +3516,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3536,7 +3533,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3550,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3564,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3578,7 +3575,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3592,7 +3589,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3606,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3620,7 +3617,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3634,7 +3631,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3648,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3659,10 +3656,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D126" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3673,10 +3670,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D127" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3690,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3704,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3718,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3732,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3746,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3760,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3774,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3788,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3799,10 +3796,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3816,7 +3813,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3830,7 +3827,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3844,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3858,7 +3855,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3872,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3883,10 +3880,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3900,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3914,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3928,7 +3925,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3942,7 +3939,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3956,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>401</v>
+        <v>343</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3970,7 +3967,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3984,7 +3981,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3998,7 +3995,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4012,7 +4009,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4026,7 +4023,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4040,7 +4037,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4051,10 +4048,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4068,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>409</v>
+        <v>277</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4082,7 +4079,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4096,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4110,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4124,7 +4121,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4138,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4152,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4163,10 +4160,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4177,10 +4174,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4194,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4208,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4222,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4236,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4250,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4264,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>423</v>
+        <v>273</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4345,7 +4342,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
         <v>429</v>
@@ -4359,7 +4356,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
         <v>430</v>
@@ -4583,7 +4580,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>446</v>
@@ -4611,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>448</v>
@@ -4625,7 +4622,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
         <v>449</v>
@@ -4793,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>461</v>
@@ -4863,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
         <v>466</v>
@@ -5003,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
         <v>476</v>
@@ -5059,7 +5056,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>480</v>
@@ -5143,7 +5140,7 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
         <v>486</v>
@@ -5216,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>491</v>
+        <v>354</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5230,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5244,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5258,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5272,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5286,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5300,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5314,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5328,7 +5325,7 @@
         <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5342,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5356,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5370,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5384,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5398,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5412,7 +5409,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5426,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5440,7 +5437,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5454,7 +5451,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>401</v>
+        <v>343</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5468,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5482,7 +5479,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
